--- a/Research_Dashboard.xlsx
+++ b/Research_Dashboard.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="379">
   <si>
     <t xml:space="preserve">Research submissions</t>
   </si>
@@ -55,7 +55,7 @@
     <t xml:space="preserve">ACCEPTED</t>
   </si>
   <si>
-    <t xml:space="preserve">excl. parked / published</t>
+    <t xml:space="preserve">excl. closed, parked, published</t>
   </si>
   <si>
     <t xml:space="preserve">to (re)submit or revise</t>
@@ -115,7 +115,7 @@
     <t xml:space="preserve">Papers sheet</t>
   </si>
   <si>
-    <t xml:space="preserve">One row per paper. Short name is the key that links to Submissions, so keep it unique. Stage is calculated. Use ‘Override’ only to park, withdraw or mark a paper as published.</t>
+    <t xml:space="preserve">One row per paper. Short name is the key that links to Submissions, so keep it unique. Stage is calculated. Use ‘Override’ only to mark a paper Closed – rejected (no plan to resubmit), Parked, Withdrawn or Published. Those drop off the ‘Waiting on you’ list.</t>
   </si>
   <si>
     <t xml:space="preserve">Submissions sheet</t>
@@ -289,6 +289,9 @@
     <t xml:space="preserve">EPW / short piece</t>
   </si>
   <si>
+    <t xml:space="preserve">Closed – rejected</t>
+  </si>
+  <si>
     <t xml:space="preserve">Algorithmic silence &amp; org. power</t>
   </si>
   <si>
@@ -388,7 +391,7 @@
     <t xml:space="preserve">India’s Workplace Engagement Crisis</t>
   </si>
   <si>
-    <t xml:space="preserve">Track at epw.in/submission-tracker</t>
+    <t xml:space="preserve">EPW-only piece; not resubmitted elsewhere</t>
   </si>
   <si>
     <t xml:space="preserve">Paper</t>
@@ -1129,22 +1132,10 @@
     <t xml:space="preserve">Old sheet says ‘Acknowledged’ with red fill, treated as closed. Check.</t>
   </si>
   <si>
-    <t xml:space="preserve">Short Fiction in Theory &amp; Practice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manoa: A Pacific Journal of International Writing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESCI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">New Writing: The International Journal for the Practice and Theory of Creative Writing</t>
-  </si>
-  <si>
     <t xml:space="preserve">EPW: Commentary</t>
   </si>
   <si>
-    <t xml:space="preserve">Acknowledged 22-Sep-25</t>
+    <t xml:space="preserve">Acknowledged 22-Sep-25; actual rejection date not recorded</t>
   </si>
   <si>
     <t xml:space="preserve">Papers</t>
@@ -1697,6 +1688,17 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFF3F4F6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF6B7280"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFEEF0F3"/>
         </patternFill>
       </fill>
@@ -1774,6 +1776,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF3F4F6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFEF0C7"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -1791,6 +1801,14 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B21B6"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF6B7280"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1822,35 +1840,8 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF3F4F6"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF6B7280"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
           <fgColor rgb="FF7C3AED"/>
           <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="FF6B7280"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF3F4F6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2047,9 +2038,9 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Calc!$A$2:$A$7</c:f>
+              <c:f>Calc!$A$2:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Revision due</c:v>
                 </c:pt>
@@ -2066,6 +2057,9 @@
                   <c:v>Accepted</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>Closed – rejected</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Parked</c:v>
                 </c:pt>
               </c:strCache>
@@ -2073,26 +2067,29 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calc!$B$2:$B$7</c:f>
+              <c:f>Calc!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>7</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
@@ -2101,11 +2098,11 @@
         </c:ser>
         <c:gapWidth val="60"/>
         <c:overlap val="0"/>
-        <c:axId val="21819148"/>
-        <c:axId val="88875264"/>
+        <c:axId val="92511276"/>
+        <c:axId val="78669583"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="21819148"/>
+        <c:axId val="92511276"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2137,7 +2134,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88875264"/>
+        <c:crossAx val="78669583"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2145,7 +2142,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88875264"/>
+        <c:axId val="78669583"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2177,7 +2174,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21819148"/>
+        <c:crossAx val="92511276"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
@@ -2510,7 +2507,7 @@
                   <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>13</c:v>
+                  <c:v>14</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>1</c:v>
@@ -2533,11 +2530,11 @@
         </c:ser>
         <c:gapWidth val="50"/>
         <c:overlap val="0"/>
-        <c:axId val="20633156"/>
-        <c:axId val="67302780"/>
+        <c:axId val="39102433"/>
+        <c:axId val="46706369"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="20633156"/>
+        <c:axId val="39102433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2569,7 +2566,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67302780"/>
+        <c:crossAx val="46706369"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2577,7 +2574,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="67302780"/>
+        <c:axId val="46706369"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2609,7 +2606,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20633156"/>
+        <c:crossAx val="39102433"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3028,18 +3025,18 @@
     <row r="6" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1"/>
       <c r="B6" s="7" t="n">
-        <f aca="false">COUNTIFS(Papers!$A$2:$A$81,"&lt;&gt;",Papers!$F$2:$F$81,"&lt;&gt;Parked",Papers!$F$2:$F$81,"&lt;&gt;Withdrawn",Papers!$F$2:$F$81,"&lt;&gt;Published")</f>
-        <v>21</v>
+        <f aca="false">COUNTIFS(Papers!$A$2:$A$81,"&lt;&gt;",Papers!$F$2:$F$81,"&lt;&gt;Parked",Papers!$F$2:$F$81,"&lt;&gt;Closed – rejected",Papers!$F$2:$F$81,"&lt;&gt;Withdrawn",Papers!$F$2:$F$81,"&lt;&gt;Published")</f>
+        <v>16</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="8" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,"Revision due")+COUNTIF(Papers!$F$2:$F$81,"Needs resubmission")+COUNTIF(Papers!$F$2:$F$81,"Not yet submitted")</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="9" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,"Under review")</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="9"/>
       <c r="H6" s="10" t="n">
@@ -3079,7 +3076,7 @@
       <c r="I7" s="12"/>
       <c r="J7" s="12" t="str">
         <f aca="false">COUNTIFS(Submissions!$D$2:$D$1000,"Rejected")+COUNTIFS(Submissions!$D$2:$D$1000,"Returned by office")&amp;" rejected or returned"</f>
-        <v>72 rejected or returned</v>
+        <v>73 rejected or returned</v>
       </c>
       <c r="K7" s="12"/>
       <c r="L7" s="12" t="str">
@@ -3156,7 +3153,7 @@
       <c r="A11" s="1"/>
       <c r="B11" s="17" t="str">
         <f aca="false">IF($O11="","",INDEX(Papers!$A$2:$A$81,$O11)&amp;"")</f>
-        <v>Faith and the Other (EPW)</v>
+        <v>Trust by Design (India engagement)</v>
       </c>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -3166,17 +3163,17 @@
       </c>
       <c r="F11" s="19" t="str">
         <f aca="false">IF($O11="","",INDEX(Papers!$G$2:$G$81,$O11)&amp;"")</f>
-        <v>EPW: Postscript</v>
+        <v>Industrial and Commercial Training</v>
       </c>
       <c r="G11" s="19"/>
       <c r="H11" s="19"/>
       <c r="I11" s="20" t="n">
         <f aca="false">IF($O11="","",INDEX(Papers!$I$2:$I$81,$O11))</f>
-        <v>607</v>
+        <v>439</v>
       </c>
       <c r="J11" s="19" t="str">
         <f aca="false">IF($O11="","",INDEX(Papers!$J$2:$J$81,$O11)&amp;"")</f>
-        <v/>
+        <v>Strategic HR Review</v>
       </c>
       <c r="K11" s="19"/>
       <c r="L11" s="19"/>
@@ -3184,14 +3181,14 @@
       <c r="N11" s="1"/>
       <c r="O11" s="21" t="n">
         <f aca="false">IFERROR(MATCH(1,Papers!$O$2:$O$81,0),"")</f>
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1"/>
       <c r="B12" s="17" t="str">
         <f aca="false">IF($O12="","",INDEX(Papers!$A$2:$A$81,$O12)&amp;"")</f>
-        <v>Trust by Design (India engagement)</v>
+        <v>Cockroach Spoke Back (Instagram, irony)</v>
       </c>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -3201,17 +3198,17 @@
       </c>
       <c r="F12" s="19" t="str">
         <f aca="false">IF($O12="","",INDEX(Papers!$G$2:$G$81,$O12)&amp;"")</f>
-        <v>Industrial and Commercial Training</v>
+        <v>Media, Culture &amp; Society</v>
       </c>
       <c r="G12" s="19"/>
       <c r="H12" s="19"/>
       <c r="I12" s="20" t="n">
         <f aca="false">IF($O12="","",INDEX(Papers!$I$2:$I$81,$O12))</f>
-        <v>439</v>
+        <v>102</v>
       </c>
       <c r="J12" s="19" t="str">
         <f aca="false">IF($O12="","",INDEX(Papers!$J$2:$J$81,$O12)&amp;"")</f>
-        <v>Strategic HR Review</v>
+        <v/>
       </c>
       <c r="K12" s="19"/>
       <c r="L12" s="19"/>
@@ -3219,14 +3216,14 @@
       <c r="N12" s="1"/>
       <c r="O12" s="21" t="n">
         <f aca="false">IFERROR(MATCH(2,Papers!$O$2:$O$81,0),"")</f>
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1"/>
       <c r="B13" s="17" t="str">
         <f aca="false">IF($O13="","",INDEX(Papers!$A$2:$A$81,$O13)&amp;"")</f>
-        <v>Enhanced Athletes (EPW Letter)</v>
+        <v>From Medium to Interlocutor (GenAI)</v>
       </c>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -3236,17 +3233,17 @@
       </c>
       <c r="F13" s="19" t="str">
         <f aca="false">IF($O13="","",INDEX(Papers!$G$2:$G$81,$O13)&amp;"")</f>
-        <v>EPW: Letter</v>
+        <v>Information, Communication &amp; Society</v>
       </c>
       <c r="G13" s="19"/>
       <c r="H13" s="19"/>
       <c r="I13" s="20" t="n">
         <f aca="false">IF($O13="","",INDEX(Papers!$I$2:$I$81,$O13))</f>
-        <v>438</v>
+        <v>1</v>
       </c>
       <c r="J13" s="19" t="str">
         <f aca="false">IF($O13="","",INDEX(Papers!$J$2:$J$81,$O13)&amp;"")</f>
-        <v/>
+        <v>Journal of Computer-Mediated Communication</v>
       </c>
       <c r="K13" s="19"/>
       <c r="L13" s="19"/>
@@ -3254,34 +3251,34 @@
       <c r="N13" s="1"/>
       <c r="O13" s="21" t="n">
         <f aca="false">IFERROR(MATCH(3,Papers!$O$2:$O$81,0),"")</f>
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1"/>
       <c r="B14" s="17" t="str">
         <f aca="false">IF($O14="","",INDEX(Papers!$A$2:$A$81,$O14)&amp;"")</f>
-        <v>Coffee with the Machine (EPW)</v>
+        <v>Distributed securitization (India SIR)</v>
       </c>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
       <c r="E14" s="18" t="str">
         <f aca="false">IF($O14="","",INDEX(Papers!$F$2:$F$81,$O14)&amp;"")</f>
-        <v>Needs resubmission</v>
+        <v>Not yet submitted</v>
       </c>
       <c r="F14" s="19" t="str">
         <f aca="false">IF($O14="","",INDEX(Papers!$G$2:$G$81,$O14)&amp;"")</f>
-        <v>EPW: Postscript</v>
+        <v/>
       </c>
       <c r="G14" s="19"/>
       <c r="H14" s="19"/>
-      <c r="I14" s="20" t="n">
+      <c r="I14" s="20" t="str">
         <f aca="false">IF($O14="","",INDEX(Papers!$I$2:$I$81,$O14))</f>
-        <v>341</v>
+        <v/>
       </c>
       <c r="J14" s="19" t="str">
         <f aca="false">IF($O14="","",INDEX(Papers!$J$2:$J$81,$O14)&amp;"")</f>
-        <v>Short Fiction in Theory &amp; Practice</v>
+        <v>Security Studies</v>
       </c>
       <c r="K14" s="19"/>
       <c r="L14" s="19"/>
@@ -3289,34 +3286,34 @@
       <c r="N14" s="1"/>
       <c r="O14" s="21" t="n">
         <f aca="false">IFERROR(MATCH(4,Papers!$O$2:$O$81,0),"")</f>
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1"/>
       <c r="B15" s="17" t="str">
         <f aca="false">IF($O15="","",INDEX(Papers!$A$2:$A$81,$O15)&amp;"")</f>
-        <v>Cockroach Spoke Back (Instagram, irony)</v>
+        <v>Right to the Secret (Blanchot–Heidegger)</v>
       </c>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
       <c r="E15" s="18" t="str">
         <f aca="false">IF($O15="","",INDEX(Papers!$F$2:$F$81,$O15)&amp;"")</f>
-        <v>Needs resubmission</v>
+        <v>Not yet submitted</v>
       </c>
       <c r="F15" s="19" t="str">
         <f aca="false">IF($O15="","",INDEX(Papers!$G$2:$G$81,$O15)&amp;"")</f>
-        <v>Media, Culture &amp; Society</v>
+        <v/>
       </c>
       <c r="G15" s="19"/>
       <c r="H15" s="19"/>
-      <c r="I15" s="20" t="n">
+      <c r="I15" s="20" t="str">
         <f aca="false">IF($O15="","",INDEX(Papers!$I$2:$I$81,$O15))</f>
-        <v>102</v>
+        <v/>
       </c>
       <c r="J15" s="19" t="str">
         <f aca="false">IF($O15="","",INDEX(Papers!$J$2:$J$81,$O15)&amp;"")</f>
-        <v/>
+        <v>Philosophy of Management</v>
       </c>
       <c r="K15" s="19"/>
       <c r="L15" s="19"/>
@@ -3324,34 +3321,34 @@
       <c r="N15" s="1"/>
       <c r="O15" s="21" t="n">
         <f aca="false">IFERROR(MATCH(5,Papers!$O$2:$O$81,0),"")</f>
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1"/>
       <c r="B16" s="17" t="str">
         <f aca="false">IF($O16="","",INDEX(Papers!$A$2:$A$81,$O16)&amp;"")</f>
-        <v>From Devta to Musafir (EPW)</v>
+        <v>Organizational Silence (lit review)</v>
       </c>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
       <c r="E16" s="18" t="str">
         <f aca="false">IF($O16="","",INDEX(Papers!$F$2:$F$81,$O16)&amp;"")</f>
-        <v>Needs resubmission</v>
+        <v>Not yet submitted</v>
       </c>
       <c r="F16" s="19" t="str">
         <f aca="false">IF($O16="","",INDEX(Papers!$G$2:$G$81,$O16)&amp;"")</f>
-        <v>EPW: Postscript</v>
+        <v/>
       </c>
       <c r="G16" s="19"/>
       <c r="H16" s="19"/>
-      <c r="I16" s="20" t="n">
+      <c r="I16" s="20" t="str">
         <f aca="false">IF($O16="","",INDEX(Papers!$I$2:$I$81,$O16))</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="J16" s="19" t="str">
         <f aca="false">IF($O16="","",INDEX(Papers!$J$2:$J$81,$O16)&amp;"")</f>
-        <v/>
+        <v>Journal of Information, Communication and Ethics in Society</v>
       </c>
       <c r="K16" s="19"/>
       <c r="L16" s="19"/>
@@ -3359,55 +3356,55 @@
       <c r="N16" s="1"/>
       <c r="O16" s="21" t="n">
         <f aca="false">IFERROR(MATCH(6,Papers!$O$2:$O$81,0),"")</f>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1"/>
       <c r="B17" s="17" t="str">
         <f aca="false">IF($O17="","",INDEX(Papers!$A$2:$A$81,$O17)&amp;"")</f>
-        <v>From Medium to Interlocutor (GenAI)</v>
+        <v/>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
       <c r="E17" s="18" t="str">
         <f aca="false">IF($O17="","",INDEX(Papers!$F$2:$F$81,$O17)&amp;"")</f>
-        <v>Needs resubmission</v>
+        <v/>
       </c>
       <c r="F17" s="19" t="str">
         <f aca="false">IF($O17="","",INDEX(Papers!$G$2:$G$81,$O17)&amp;"")</f>
-        <v>Information, Communication &amp; Society</v>
+        <v/>
       </c>
       <c r="G17" s="19"/>
       <c r="H17" s="19"/>
-      <c r="I17" s="20" t="n">
+      <c r="I17" s="20" t="str">
         <f aca="false">IF($O17="","",INDEX(Papers!$I$2:$I$81,$O17))</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="J17" s="19" t="str">
         <f aca="false">IF($O17="","",INDEX(Papers!$J$2:$J$81,$O17)&amp;"")</f>
-        <v>Journal of Computer-Mediated Communication</v>
+        <v/>
       </c>
       <c r="K17" s="19"/>
       <c r="L17" s="19"/>
       <c r="M17" s="19"/>
       <c r="N17" s="1"/>
-      <c r="O17" s="21" t="n">
+      <c r="O17" s="0" t="str">
         <f aca="false">IFERROR(MATCH(7,Papers!$O$2:$O$81,0),"")</f>
-        <v>11</v>
+        <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1"/>
       <c r="B18" s="17" t="str">
         <f aca="false">IF($O18="","",INDEX(Papers!$A$2:$A$81,$O18)&amp;"")</f>
-        <v>Distributed securitization (India SIR)</v>
+        <v/>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
       <c r="E18" s="18" t="str">
         <f aca="false">IF($O18="","",INDEX(Papers!$F$2:$F$81,$O18)&amp;"")</f>
-        <v>Not yet submitted</v>
+        <v/>
       </c>
       <c r="F18" s="19" t="str">
         <f aca="false">IF($O18="","",INDEX(Papers!$G$2:$G$81,$O18)&amp;"")</f>
@@ -3421,28 +3418,28 @@
       </c>
       <c r="J18" s="19" t="str">
         <f aca="false">IF($O18="","",INDEX(Papers!$J$2:$J$81,$O18)&amp;"")</f>
-        <v>Security Studies</v>
+        <v/>
       </c>
       <c r="K18" s="19"/>
       <c r="L18" s="19"/>
       <c r="M18" s="19"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="21" t="n">
+      <c r="O18" s="0" t="str">
         <f aca="false">IFERROR(MATCH(8,Papers!$O$2:$O$81,0),"")</f>
-        <v>6</v>
+        <v/>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1"/>
       <c r="B19" s="17" t="str">
         <f aca="false">IF($O19="","",INDEX(Papers!$A$2:$A$81,$O19)&amp;"")</f>
-        <v>Right to the Secret (Blanchot–Heidegger)</v>
+        <v/>
       </c>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
       <c r="E19" s="18" t="str">
         <f aca="false">IF($O19="","",INDEX(Papers!$F$2:$F$81,$O19)&amp;"")</f>
-        <v>Not yet submitted</v>
+        <v/>
       </c>
       <c r="F19" s="19" t="str">
         <f aca="false">IF($O19="","",INDEX(Papers!$G$2:$G$81,$O19)&amp;"")</f>
@@ -3456,28 +3453,28 @@
       </c>
       <c r="J19" s="19" t="str">
         <f aca="false">IF($O19="","",INDEX(Papers!$J$2:$J$81,$O19)&amp;"")</f>
-        <v>Philosophy of Management</v>
+        <v/>
       </c>
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
       <c r="M19" s="19"/>
       <c r="N19" s="1"/>
-      <c r="O19" s="21" t="n">
+      <c r="O19" s="0" t="str">
         <f aca="false">IFERROR(MATCH(9,Papers!$O$2:$O$81,0),"")</f>
-        <v>12</v>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1"/>
       <c r="B20" s="17" t="str">
         <f aca="false">IF($O20="","",INDEX(Papers!$A$2:$A$81,$O20)&amp;"")</f>
-        <v>Organizational Silence (lit review)</v>
+        <v/>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
       <c r="E20" s="18" t="str">
         <f aca="false">IF($O20="","",INDEX(Papers!$F$2:$F$81,$O20)&amp;"")</f>
-        <v>Not yet submitted</v>
+        <v/>
       </c>
       <c r="F20" s="19" t="str">
         <f aca="false">IF($O20="","",INDEX(Papers!$G$2:$G$81,$O20)&amp;"")</f>
@@ -3491,15 +3488,15 @@
       </c>
       <c r="J20" s="19" t="str">
         <f aca="false">IF($O20="","",INDEX(Papers!$J$2:$J$81,$O20)&amp;"")</f>
-        <v>Journal of Information, Communication and Ethics in Society</v>
+        <v/>
       </c>
       <c r="K20" s="19"/>
       <c r="L20" s="19"/>
       <c r="M20" s="19"/>
       <c r="N20" s="1"/>
-      <c r="O20" s="21" t="n">
+      <c r="O20" s="0" t="str">
         <f aca="false">IFERROR(MATCH(10,Papers!$O$2:$O$81,0),"")</f>
-        <v>13</v>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3674,24 +3671,24 @@
       <c r="A27" s="1"/>
       <c r="B27" s="17" t="str">
         <f aca="false">IF($O27="","",INDEX(Submissions!$A$2:$A$1000,$O27)&amp;"")</f>
-        <v>India’s Workplace Engagement Crisis (EPW)</v>
+        <v>Farmers’ protest &amp; radical passivity</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
       <c r="E27" s="19" t="str">
         <f aca="false">IF($O27="","",INDEX(Submissions!$B$2:$B$1000,$O27)&amp;"")</f>
-        <v>EPW: Commentary</v>
+        <v>Applied Linguistics</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
       <c r="H27" s="19"/>
       <c r="I27" s="22" t="n">
         <f aca="false">IF($O27="","",INDEX(Submissions!$E$2:$E$1000,$O27))</f>
-        <v>45907</v>
+        <v>46045</v>
       </c>
       <c r="J27" s="20" t="n">
         <f aca="false">IF($O27="","",INDEX(Submissions!$G$2:$G$1000,$O27))</f>
-        <v>399</v>
+        <v>261</v>
       </c>
       <c r="K27" s="23" t="str">
         <f aca="false">IF($O27="","",IF(J27&gt;=2*$M$3,"Overdue: chase editor",IF(J27&gt;=$M$3,"Check status","")))</f>
@@ -3702,101 +3699,101 @@
       <c r="N27" s="1"/>
       <c r="O27" s="21" t="n">
         <f aca="false">IFERROR(MATCH(2,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>187</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1"/>
       <c r="B28" s="17" t="str">
         <f aca="false">IF($O28="","",INDEX(Submissions!$A$2:$A$1000,$O28)&amp;"")</f>
-        <v>Farmers’ protest &amp; radical passivity</v>
+        <v>Algorithmic silence &amp; org. power</v>
       </c>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
       <c r="E28" s="19" t="str">
         <f aca="false">IF($O28="","",INDEX(Submissions!$B$2:$B$1000,$O28)&amp;"")</f>
-        <v>Applied Linguistics</v>
+        <v>Organization Theory</v>
       </c>
       <c r="F28" s="19"/>
       <c r="G28" s="19"/>
       <c r="H28" s="19"/>
       <c r="I28" s="22" t="n">
         <f aca="false">IF($O28="","",INDEX(Submissions!$E$2:$E$1000,$O28))</f>
-        <v>46045</v>
+        <v>46153</v>
       </c>
       <c r="J28" s="20" t="n">
         <f aca="false">IF($O28="","",INDEX(Submissions!$G$2:$G$1000,$O28))</f>
-        <v>261</v>
+        <v>153</v>
       </c>
       <c r="K28" s="23" t="str">
         <f aca="false">IF($O28="","",IF(J28&gt;=2*$M$3,"Overdue: chase editor",IF(J28&gt;=$M$3,"Check status","")))</f>
-        <v>Overdue: chase editor</v>
+        <v>Check status</v>
       </c>
       <c r="L28" s="23"/>
       <c r="M28" s="23"/>
       <c r="N28" s="1"/>
       <c r="O28" s="21" t="n">
         <f aca="false">IFERROR(MATCH(3,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>135</v>
+        <v>78</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1"/>
       <c r="B29" s="17" t="str">
         <f aca="false">IF($O29="","",INDEX(Submissions!$A$2:$A$1000,$O29)&amp;"")</f>
-        <v>Algorithmic silence &amp; org. power</v>
+        <v>Intentional tacit knowledge hiding (Malawi)</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
       <c r="E29" s="19" t="str">
         <f aca="false">IF($O29="","",INDEX(Submissions!$B$2:$B$1000,$O29)&amp;"")</f>
-        <v>Organization Theory</v>
+        <v>Global Knowledge, Memory and Communication</v>
       </c>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="22" t="n">
         <f aca="false">IF($O29="","",INDEX(Submissions!$E$2:$E$1000,$O29))</f>
-        <v>46153</v>
+        <v>46232</v>
       </c>
       <c r="J29" s="20" t="n">
         <f aca="false">IF($O29="","",INDEX(Submissions!$G$2:$G$1000,$O29))</f>
-        <v>153</v>
+        <v>74</v>
       </c>
       <c r="K29" s="23" t="str">
         <f aca="false">IF($O29="","",IF(J29&gt;=2*$M$3,"Overdue: chase editor",IF(J29&gt;=$M$3,"Check status","")))</f>
-        <v>Check status</v>
+        <v/>
       </c>
       <c r="L29" s="23"/>
       <c r="M29" s="23"/>
       <c r="N29" s="1"/>
       <c r="O29" s="21" t="n">
         <f aca="false">IFERROR(MATCH(4,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>78</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1"/>
       <c r="B30" s="17" t="str">
         <f aca="false">IF($O30="","",INDEX(Submissions!$A$2:$A$1000,$O30)&amp;"")</f>
-        <v>Intentional tacit knowledge hiding (Malawi)</v>
+        <v>Derrida hauntology &amp; memory ethics</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
       <c r="E30" s="19" t="str">
         <f aca="false">IF($O30="","",INDEX(Submissions!$B$2:$B$1000,$O30)&amp;"")</f>
-        <v>Global Knowledge, Memory and Communication</v>
+        <v>Time and Society</v>
       </c>
       <c r="F30" s="19"/>
       <c r="G30" s="19"/>
       <c r="H30" s="19"/>
       <c r="I30" s="22" t="n">
         <f aca="false">IF($O30="","",INDEX(Submissions!$E$2:$E$1000,$O30))</f>
-        <v>46232</v>
+        <v>46289</v>
       </c>
       <c r="J30" s="20" t="n">
         <f aca="false">IF($O30="","",INDEX(Submissions!$G$2:$G$1000,$O30))</f>
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="K30" s="23" t="str">
         <f aca="false">IF($O30="","",IF(J30&gt;=2*$M$3,"Overdue: chase editor",IF(J30&gt;=$M$3,"Check status","")))</f>
@@ -3807,31 +3804,31 @@
       <c r="N30" s="1"/>
       <c r="O30" s="21" t="n">
         <f aca="false">IFERROR(MATCH(5,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>98</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1"/>
       <c r="B31" s="17" t="str">
         <f aca="false">IF($O31="","",INDEX(Submissions!$A$2:$A$1000,$O31)&amp;"")</f>
-        <v>Derrida hauntology &amp; memory ethics</v>
+        <v>‘One dies’: Blanchot &amp; organizational speech</v>
       </c>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
       <c r="E31" s="19" t="str">
         <f aca="false">IF($O31="","",INDEX(Submissions!$B$2:$B$1000,$O31)&amp;"")</f>
-        <v>Time and Society</v>
+        <v>Organization</v>
       </c>
       <c r="F31" s="19"/>
       <c r="G31" s="19"/>
       <c r="H31" s="19"/>
       <c r="I31" s="22" t="n">
         <f aca="false">IF($O31="","",INDEX(Submissions!$E$2:$E$1000,$O31))</f>
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="J31" s="20" t="n">
         <f aca="false">IF($O31="","",INDEX(Submissions!$G$2:$G$1000,$O31))</f>
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="K31" s="23" t="str">
         <f aca="false">IF($O31="","",IF(J31&gt;=2*$M$3,"Overdue: chase editor",IF(J31&gt;=$M$3,"Check status","")))</f>
@@ -3842,31 +3839,31 @@
       <c r="N31" s="1"/>
       <c r="O31" s="21" t="n">
         <f aca="false">IFERROR(MATCH(6,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1"/>
       <c r="B32" s="17" t="str">
         <f aca="false">IF($O32="","",INDEX(Submissions!$A$2:$A$1000,$O32)&amp;"")</f>
-        <v>‘One dies’: Blanchot &amp; organizational speech</v>
+        <v>Is Leadership Inherently Violent?</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
       <c r="E32" s="19" t="str">
         <f aca="false">IF($O32="","",INDEX(Submissions!$B$2:$B$1000,$O32)&amp;"")</f>
-        <v>Organization</v>
+        <v>Journal of Business Ethics</v>
       </c>
       <c r="F32" s="19"/>
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="22" t="n">
         <f aca="false">IF($O32="","",INDEX(Submissions!$E$2:$E$1000,$O32))</f>
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="J32" s="20" t="n">
         <f aca="false">IF($O32="","",INDEX(Submissions!$G$2:$G$1000,$O32))</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K32" s="23" t="str">
         <f aca="false">IF($O32="","",IF(J32&gt;=2*$M$3,"Overdue: chase editor",IF(J32&gt;=$M$3,"Check status","")))</f>
@@ -3877,20 +3874,20 @@
       <c r="N32" s="1"/>
       <c r="O32" s="21" t="n">
         <f aca="false">IFERROR(MATCH(7,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>15</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1"/>
       <c r="B33" s="17" t="str">
         <f aca="false">IF($O33="","",INDEX(Submissions!$A$2:$A$1000,$O33)&amp;"")</f>
-        <v>Is Leadership Inherently Violent?</v>
+        <v>Cockroaches, Not Citizens (CDA)</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
       <c r="E33" s="19" t="str">
         <f aca="false">IF($O33="","",INDEX(Submissions!$B$2:$B$1000,$O33)&amp;"")</f>
-        <v>Journal of Business Ethics</v>
+        <v>Discourse &amp; Communication</v>
       </c>
       <c r="F33" s="19"/>
       <c r="G33" s="19"/>
@@ -3912,31 +3909,31 @@
       <c r="N33" s="1"/>
       <c r="O33" s="21" t="n">
         <f aca="false">IFERROR(MATCH(8,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>160</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1"/>
       <c r="B34" s="17" t="str">
         <f aca="false">IF($O34="","",INDEX(Submissions!$A$2:$A$1000,$O34)&amp;"")</f>
-        <v>Cockroaches, Not Citizens (CDA)</v>
+        <v>Bullshit without a bullshitter (GenAI)</v>
       </c>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
       <c r="E34" s="19" t="str">
         <f aca="false">IF($O34="","",INDEX(Submissions!$B$2:$B$1000,$O34)&amp;"")</f>
-        <v>Discourse &amp; Communication</v>
+        <v>Journal of Management Studies</v>
       </c>
       <c r="F34" s="19"/>
       <c r="G34" s="19"/>
       <c r="H34" s="19"/>
       <c r="I34" s="22" t="n">
         <f aca="false">IF($O34="","",INDEX(Submissions!$E$2:$E$1000,$O34))</f>
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="J34" s="20" t="n">
         <f aca="false">IF($O34="","",INDEX(Submissions!$G$2:$G$1000,$O34))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K34" s="23" t="str">
         <f aca="false">IF($O34="","",IF(J34&gt;=2*$M$3,"Overdue: chase editor",IF(J34&gt;=$M$3,"Check status","")))</f>
@@ -3947,31 +3944,31 @@
       <c r="N34" s="1"/>
       <c r="O34" s="21" t="n">
         <f aca="false">IFERROR(MATCH(9,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1"/>
       <c r="B35" s="17" t="str">
         <f aca="false">IF($O35="","",INDEX(Submissions!$A$2:$A$1000,$O35)&amp;"")</f>
-        <v>Bullshit without a bullshitter (GenAI)</v>
+        <v>Cosmoceuticals</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
       <c r="E35" s="19" t="str">
         <f aca="false">IF($O35="","",INDEX(Submissions!$B$2:$B$1000,$O35)&amp;"")</f>
-        <v>Journal of Management Studies</v>
+        <v>IEEE Transactions on Engineering Management</v>
       </c>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
       <c r="H35" s="19"/>
       <c r="I35" s="22" t="n">
         <f aca="false">IF($O35="","",INDEX(Submissions!$E$2:$E$1000,$O35))</f>
-        <v>46301</v>
+        <v>46303</v>
       </c>
       <c r="J35" s="20" t="n">
         <f aca="false">IF($O35="","",INDEX(Submissions!$G$2:$G$1000,$O35))</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K35" s="23" t="str">
         <f aca="false">IF($O35="","",IF(J35&gt;=2*$M$3,"Overdue: chase editor",IF(J35&gt;=$M$3,"Check status","")))</f>
@@ -3982,31 +3979,31 @@
       <c r="N35" s="1"/>
       <c r="O35" s="21" t="n">
         <f aca="false">IFERROR(MATCH(10,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>68</v>
+        <v>169</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1"/>
       <c r="B36" s="17" t="str">
         <f aca="false">IF($O36="","",INDEX(Submissions!$A$2:$A$1000,$O36)&amp;"")</f>
-        <v>Cosmoceuticals</v>
+        <v/>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
       <c r="E36" s="19" t="str">
         <f aca="false">IF($O36="","",INDEX(Submissions!$B$2:$B$1000,$O36)&amp;"")</f>
-        <v>IEEE Transactions on Engineering Management</v>
+        <v/>
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
-      <c r="I36" s="22" t="n">
+      <c r="I36" s="22" t="str">
         <f aca="false">IF($O36="","",INDEX(Submissions!$E$2:$E$1000,$O36))</f>
-        <v>46303</v>
-      </c>
-      <c r="J36" s="20" t="n">
+        <v/>
+      </c>
+      <c r="J36" s="20" t="str">
         <f aca="false">IF($O36="","",INDEX(Submissions!$G$2:$G$1000,$O36))</f>
-        <v>3</v>
+        <v/>
       </c>
       <c r="K36" s="23" t="str">
         <f aca="false">IF($O36="","",IF(J36&gt;=2*$M$3,"Overdue: chase editor",IF(J36&gt;=$M$3,"Check status","")))</f>
@@ -4015,9 +4012,9 @@
       <c r="L36" s="23"/>
       <c r="M36" s="23"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="21" t="n">
+      <c r="O36" s="0" t="str">
         <f aca="false">IFERROR(MATCH(11,Submissions!$O$2:$O$1000,0),"")</f>
-        <v>169</v>
+        <v/>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4738,43 +4735,46 @@
       <formula>$E11="Accepted"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>$E11="Closed – rejected"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$E11="Parked"</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>$E11="Published"</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$E11="Withdrawn"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I11:I22">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND(ISNUMBER($I11),$I11&gt;=180)</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>AND(ISNUMBER($I11),$I11&gt;=60)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:M22">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$O11&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K26:M39">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$K26="Overdue: chase editor"</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>$K26="Check status"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J26:J39">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND(ISNUMBER($J26),$J26&gt;=2*$M$3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B26:M39">
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$O26&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5208,7 +5208,7 @@
       </c>
       <c r="O5" s="32" t="n">
         <f aca="false">IF($N5="","",RANK($N5,$N$2:$N$81))</f>
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="O7" s="32" t="n">
         <f aca="false">IF($N7="","",RANK($N7,$N$2:$N$81))</f>
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5372,10 +5372,12 @@
       <c r="D9" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="29"/>
+      <c r="E9" s="29" t="s">
+        <v>86</v>
+      </c>
       <c r="F9" s="29" t="str">
         <f aca="false">IF($A9="","",IF($E9&lt;&gt;"",$E9,IF(COUNTIFS(Submissions!$A$2:$A$1000,$A9,Submissions!$D$2:$D$1000,"Accepted")&gt;0,"Accepted",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A9,Submissions!$D$2:$D$1000,"Revision requested")&gt;0,"Revision due",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A9,Submissions!$D$2:$D$1000,"Under review")&gt;0,"Under review",IF($K9&gt;0,"Needs resubmission","Not yet submitted"))))))</f>
-        <v>Needs resubmission</v>
+        <v>Closed – rejected</v>
       </c>
       <c r="G9" s="29" t="str">
         <f aca="false">IF($A9="","",IFERROR(INDEX(Submissions!$B$2:$B$1000,MATCH(_xlfn.MAXIFS(Submissions!$L$2:$L$1000,Submissions!$A$2:$A$1000,$A9),Submissions!$L$2:$L$1000,0)),""))</f>
@@ -5385,9 +5387,9 @@
         <f aca="false">IF($A9="","",IF(_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A9)=0,"",_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A9)))</f>
         <v>46298</v>
       </c>
-      <c r="I9" s="29" t="n">
+      <c r="I9" s="29" t="str">
         <f aca="true">IF($F9="Needs resubmission",IF($H9="","",TODAY()-$H9),"")</f>
-        <v>8</v>
+        <v/>
       </c>
       <c r="J9" s="29" t="str">
         <f aca="false">IF($A9="","",IF(_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A9)=0,"",INDEX(Submissions!$B$2:$B$1000,_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A9)-1)))</f>
@@ -5402,21 +5404,21 @@
         <v>1</v>
       </c>
       <c r="M9" s="30"/>
-      <c r="N9" s="32" t="n">
+      <c r="N9" s="32" t="str">
         <f aca="false">IF(IF($F9="Revision due",3000,IF($F9="Needs resubmission",2000,IF($F9="Not yet submitted",1000,"")))="","",IF($F9="Revision due",3000,IF($F9="Needs resubmission",2000,IF($F9="Not yet submitted",1000,"")))+IF($I9="",0,MIN($I9,999))+(1000-ROW())/100000)</f>
-        <v>2008.00991</v>
-      </c>
-      <c r="O9" s="32" t="n">
+        <v/>
+      </c>
+      <c r="O9" s="32" t="str">
         <f aca="false">IF($N9="","",RANK($N9,$N$2:$N$81))</f>
-        <v>6</v>
+        <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="29" t="s">
         <v>67</v>
@@ -5454,7 +5456,7 @@
         <v>7</v>
       </c>
       <c r="M10" s="30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N10" s="32" t="str">
         <f aca="false">IF(IF($F10="Revision due",3000,IF($F10="Needs resubmission",2000,IF($F10="Not yet submitted",1000,"")))="","",IF($F10="Revision due",3000,IF($F10="Needs resubmission",2000,IF($F10="Not yet submitted",1000,"")))+IF($I10="",0,MIN($I10,999))+(1000-ROW())/100000)</f>
@@ -5467,13 +5469,13 @@
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" s="29" t="s">
         <v>68</v>
@@ -5508,7 +5510,7 @@
         <v>10</v>
       </c>
       <c r="M11" s="30" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N11" s="32" t="str">
         <f aca="false">IF(IF($F11="Revision due",3000,IF($F11="Needs resubmission",2000,IF($F11="Not yet submitted",1000,"")))="","",IF($F11="Revision due",3000,IF($F11="Needs resubmission",2000,IF($F11="Not yet submitted",1000,"")))+IF($I11="",0,MIN($I11,999))+(1000-ROW())/100000)</f>
@@ -5521,13 +5523,13 @@
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D12" s="29" t="s">
         <v>68</v>
@@ -5562,7 +5564,7 @@
         <v>5</v>
       </c>
       <c r="M12" s="30" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N12" s="32" t="n">
         <f aca="false">IF(IF($F12="Revision due",3000,IF($F12="Needs resubmission",2000,IF($F12="Not yet submitted",1000,"")))="","",IF($F12="Revision due",3000,IF($F12="Needs resubmission",2000,IF($F12="Not yet submitted",1000,"")))+IF($I12="",0,MIN($I12,999))+(1000-ROW())/100000)</f>
@@ -5570,15 +5572,15 @@
       </c>
       <c r="O12" s="32" t="n">
         <f aca="false">IF($N12="","",RANK($N12,$N$2:$N$81))</f>
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C13" s="29"/>
       <c r="D13" s="29" t="s">
@@ -5620,15 +5622,15 @@
       </c>
       <c r="O13" s="32" t="n">
         <f aca="false">IF($N13="","",RANK($N13,$N$2:$N$81))</f>
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C14" s="29"/>
       <c r="D14" s="29" t="s">
@@ -5664,7 +5666,7 @@
         <v>0</v>
       </c>
       <c r="M14" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N14" s="32" t="n">
         <f aca="false">IF(IF($F14="Revision due",3000,IF($F14="Needs resubmission",2000,IF($F14="Not yet submitted",1000,"")))="","",IF($F14="Revision due",3000,IF($F14="Needs resubmission",2000,IF($F14="Not yet submitted",1000,"")))+IF($I14="",0,MIN($I14,999))+(1000-ROW())/100000)</f>
@@ -5672,15 +5674,15 @@
       </c>
       <c r="O14" s="32" t="n">
         <f aca="false">IF($N14="","",RANK($N14,$N$2:$N$81))</f>
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C15" s="29" t="s">
         <v>67</v>
@@ -5718,7 +5720,7 @@
         <v>14</v>
       </c>
       <c r="M15" s="30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N15" s="32" t="str">
         <f aca="false">IF(IF($F15="Revision due",3000,IF($F15="Needs resubmission",2000,IF($F15="Not yet submitted",1000,"")))="","",IF($F15="Revision due",3000,IF($F15="Needs resubmission",2000,IF($F15="Not yet submitted",1000,"")))+IF($I15="",0,MIN($I15,999))+(1000-ROW())/100000)</f>
@@ -5731,10 +5733,10 @@
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="29" t="s">
         <v>67</v>
@@ -5778,15 +5780,15 @@
       </c>
       <c r="O16" s="32" t="n">
         <f aca="false">IF($N16="","",RANK($N16,$N$2:$N$81))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17" s="29" t="s">
         <v>67</v>
@@ -5835,10 +5837,10 @@
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B18" s="30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="29" t="s">
@@ -5874,7 +5876,7 @@
         <v>2</v>
       </c>
       <c r="M18" s="30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N18" s="32" t="str">
         <f aca="false">IF(IF($F18="Revision due",3000,IF($F18="Needs resubmission",2000,IF($F18="Not yet submitted",1000,"")))="","",IF($F18="Revision due",3000,IF($F18="Needs resubmission",2000,IF($F18="Not yet submitted",1000,"")))+IF($I18="",0,MIN($I18,999))+(1000-ROW())/100000)</f>
@@ -5887,19 +5889,21 @@
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="29"/>
+      <c r="E19" s="29" t="s">
+        <v>86</v>
+      </c>
       <c r="F19" s="29" t="str">
         <f aca="false">IF($A19="","",IF($E19&lt;&gt;"",$E19,IF(COUNTIFS(Submissions!$A$2:$A$1000,$A19,Submissions!$D$2:$D$1000,"Accepted")&gt;0,"Accepted",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A19,Submissions!$D$2:$D$1000,"Revision requested")&gt;0,"Revision due",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A19,Submissions!$D$2:$D$1000,"Under review")&gt;0,"Under review",IF($K19&gt;0,"Needs resubmission","Not yet submitted"))))))</f>
-        <v>Needs resubmission</v>
+        <v>Closed – rejected</v>
       </c>
       <c r="G19" s="29" t="str">
         <f aca="false">IF($A19="","",IFERROR(INDEX(Submissions!$B$2:$B$1000,MATCH(_xlfn.MAXIFS(Submissions!$L$2:$L$1000,Submissions!$A$2:$A$1000,$A19),Submissions!$L$2:$L$1000,0)),""))</f>
@@ -5909,9 +5913,9 @@
         <f aca="false">IF($A19="","",IF(_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A19)=0,"",_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A19)))</f>
         <v>45868</v>
       </c>
-      <c r="I19" s="29" t="n">
+      <c r="I19" s="29" t="str">
         <f aca="true">IF($F19="Needs resubmission",IF($H19="","",TODAY()-$H19),"")</f>
-        <v>438</v>
+        <v/>
       </c>
       <c r="J19" s="29" t="str">
         <f aca="false">IF($A19="","",IF(_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A19)=0,"",INDEX(Submissions!$B$2:$B$1000,_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A19)-1)))</f>
@@ -5926,30 +5930,32 @@
         <v>1</v>
       </c>
       <c r="M19" s="30"/>
-      <c r="N19" s="32" t="n">
+      <c r="N19" s="32" t="str">
         <f aca="false">IF(IF($F19="Revision due",3000,IF($F19="Needs resubmission",2000,IF($F19="Not yet submitted",1000,"")))="","",IF($F19="Revision due",3000,IF($F19="Needs resubmission",2000,IF($F19="Not yet submitted",1000,"")))+IF($I19="",0,MIN($I19,999))+(1000-ROW())/100000)</f>
-        <v>2438.00981</v>
-      </c>
-      <c r="O19" s="32" t="n">
+        <v/>
+      </c>
+      <c r="O19" s="32" t="str">
         <f aca="false">IF($N19="","",RANK($N19,$N$2:$N$81))</f>
-        <v>3</v>
+        <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B20" s="30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C20" s="29"/>
       <c r="D20" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E20" s="29"/>
+      <c r="E20" s="29" t="s">
+        <v>86</v>
+      </c>
       <c r="F20" s="29" t="str">
         <f aca="false">IF($A20="","",IF($E20&lt;&gt;"",$E20,IF(COUNTIFS(Submissions!$A$2:$A$1000,$A20,Submissions!$D$2:$D$1000,"Accepted")&gt;0,"Accepted",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A20,Submissions!$D$2:$D$1000,"Revision requested")&gt;0,"Revision due",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A20,Submissions!$D$2:$D$1000,"Under review")&gt;0,"Under review",IF($K20&gt;0,"Needs resubmission","Not yet submitted"))))))</f>
-        <v>Needs resubmission</v>
+        <v>Closed – rejected</v>
       </c>
       <c r="G20" s="29" t="str">
         <f aca="false">IF($A20="","",IFERROR(INDEX(Submissions!$B$2:$B$1000,MATCH(_xlfn.MAXIFS(Submissions!$L$2:$L$1000,Submissions!$A$2:$A$1000,$A20),Submissions!$L$2:$L$1000,0)),""))</f>
@@ -5959,9 +5965,9 @@
         <f aca="false">IF($A20="","",IF(_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A20)=0,"",_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A20)))</f>
         <v>45699</v>
       </c>
-      <c r="I20" s="29" t="n">
+      <c r="I20" s="29" t="str">
         <f aca="true">IF($F20="Needs resubmission",IF($H20="","",TODAY()-$H20),"")</f>
-        <v>607</v>
+        <v/>
       </c>
       <c r="J20" s="29" t="str">
         <f aca="false">IF($A20="","",IF(_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A20)=0,"",INDEX(Submissions!$B$2:$B$1000,_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A20)-1)))</f>
@@ -5976,30 +5982,32 @@
         <v>1</v>
       </c>
       <c r="M20" s="30"/>
-      <c r="N20" s="32" t="n">
+      <c r="N20" s="32" t="str">
         <f aca="false">IF(IF($F20="Revision due",3000,IF($F20="Needs resubmission",2000,IF($F20="Not yet submitted",1000,"")))="","",IF($F20="Revision due",3000,IF($F20="Needs resubmission",2000,IF($F20="Not yet submitted",1000,"")))+IF($I20="",0,MIN($I20,999))+(1000-ROW())/100000)</f>
-        <v>2607.0098</v>
-      </c>
-      <c r="O20" s="32" t="n">
+        <v/>
+      </c>
+      <c r="O20" s="32" t="str">
         <f aca="false">IF($N20="","",RANK($N20,$N$2:$N$81))</f>
-        <v>1</v>
+        <v/>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B21" s="30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="29"/>
+      <c r="E21" s="29" t="s">
+        <v>86</v>
+      </c>
       <c r="F21" s="29" t="str">
         <f aca="false">IF($A21="","",IF($E21&lt;&gt;"",$E21,IF(COUNTIFS(Submissions!$A$2:$A$1000,$A21,Submissions!$D$2:$D$1000,"Accepted")&gt;0,"Accepted",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A21,Submissions!$D$2:$D$1000,"Revision requested")&gt;0,"Revision due",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A21,Submissions!$D$2:$D$1000,"Under review")&gt;0,"Under review",IF($K21&gt;0,"Needs resubmission","Not yet submitted"))))))</f>
-        <v>Needs resubmission</v>
+        <v>Closed – rejected</v>
       </c>
       <c r="G21" s="29" t="str">
         <f aca="false">IF($A21="","",IFERROR(INDEX(Submissions!$B$2:$B$1000,MATCH(_xlfn.MAXIFS(Submissions!$L$2:$L$1000,Submissions!$A$2:$A$1000,$A21),Submissions!$L$2:$L$1000,0)),""))</f>
@@ -6009,13 +6017,13 @@
         <f aca="false">IF($A21="","",IF(_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A21)=0,"",_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A21)))</f>
         <v>45965</v>
       </c>
-      <c r="I21" s="29" t="n">
+      <c r="I21" s="29" t="str">
         <f aca="true">IF($F21="Needs resubmission",IF($H21="","",TODAY()-$H21),"")</f>
-        <v>341</v>
+        <v/>
       </c>
       <c r="J21" s="29" t="str">
         <f aca="false">IF($A21="","",IF(_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A21)=0,"",INDEX(Submissions!$B$2:$B$1000,_xlfn.MINIFS(Submissions!$M$2:$M$1000,Submissions!$A$2:$A$1000,$A21)-1)))</f>
-        <v>Short Fiction in Theory &amp; Practice</v>
+        <v/>
       </c>
       <c r="K21" s="29" t="n">
         <f aca="false">IF($A21="","",SUMIFS(Submissions!$J$2:$J$1000,Submissions!$A$2:$A$1000,$A21))</f>
@@ -6026,38 +6034,40 @@
         <v>1</v>
       </c>
       <c r="M21" s="30"/>
-      <c r="N21" s="32" t="n">
+      <c r="N21" s="32" t="str">
         <f aca="false">IF(IF($F21="Revision due",3000,IF($F21="Needs resubmission",2000,IF($F21="Not yet submitted",1000,"")))="","",IF($F21="Revision due",3000,IF($F21="Needs resubmission",2000,IF($F21="Not yet submitted",1000,"")))+IF($I21="",0,MIN($I21,999))+(1000-ROW())/100000)</f>
-        <v>2341.00979</v>
-      </c>
-      <c r="O21" s="32" t="n">
+        <v/>
+      </c>
+      <c r="O21" s="32" t="str">
         <f aca="false">IF($N21="","",RANK($N21,$N$2:$N$81))</f>
-        <v>4</v>
+        <v/>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" s="30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C22" s="29"/>
       <c r="D22" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="29"/>
+      <c r="E22" s="29" t="s">
+        <v>86</v>
+      </c>
       <c r="F22" s="29" t="str">
         <f aca="false">IF($A22="","",IF($E22&lt;&gt;"",$E22,IF(COUNTIFS(Submissions!$A$2:$A$1000,$A22,Submissions!$D$2:$D$1000,"Accepted")&gt;0,"Accepted",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A22,Submissions!$D$2:$D$1000,"Revision requested")&gt;0,"Revision due",IF(COUNTIFS(Submissions!$A$2:$A$1000,$A22,Submissions!$D$2:$D$1000,"Under review")&gt;0,"Under review",IF($K22&gt;0,"Needs resubmission","Not yet submitted"))))))</f>
-        <v>Under review</v>
+        <v>Closed – rejected</v>
       </c>
       <c r="G22" s="29" t="str">
         <f aca="false">IF($A22="","",IFERROR(INDEX(Submissions!$B$2:$B$1000,MATCH(_xlfn.MAXIFS(Submissions!$L$2:$L$1000,Submissions!$A$2:$A$1000,$A22),Submissions!$L$2:$L$1000,0)),""))</f>
         <v>EPW: Commentary</v>
       </c>
-      <c r="H22" s="31" t="str">
+      <c r="H22" s="31" t="n">
         <f aca="false">IF($A22="","",IF(_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A22)=0,"",_xlfn.MAXIFS(Submissions!$F$2:$F$1000,Submissions!$A$2:$A$1000,$A22)))</f>
-        <v/>
+        <v>45922</v>
       </c>
       <c r="I22" s="29" t="str">
         <f aca="true">IF($F22="Needs resubmission",IF($H22="","",TODAY()-$H22),"")</f>
@@ -6073,10 +6083,10 @@
       </c>
       <c r="L22" s="29" t="n">
         <f aca="false">IF($A22="","",COUNTIFS(Submissions!$A$2:$A$1000,$A22,Submissions!$D$2:$D$1000,"Rejected")+COUNTIFS(Submissions!$A$2:$A$1000,$A22,Submissions!$D$2:$D$1000,"Returned by office"))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" s="30" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N22" s="32" t="str">
         <f aca="false">IF(IF($F22="Revision due",3000,IF($F22="Needs resubmission",2000,IF($F22="Not yet submitted",1000,"")))="","",IF($F22="Revision due",3000,IF($F22="Needs resubmission",2000,IF($F22="Not yet submitted",1000,"")))+IF($I22="",0,MIN($I22,999))+(1000-ROW())/100000)</f>
@@ -8702,26 +8712,29 @@
       <formula>"Accepted"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>"Closed – rejected"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Parked"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>"Published"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="cellIs" priority="10" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>"Withdrawn"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I81">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND(ISNUMBER($I2),$I2&gt;=180)</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>AND(ISNUMBER($I2),$I2&gt;=60)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E2:E81" type="list">
-      <formula1>"Parked,Published,Withdrawn"</formula1>
+      <formula1>"Closed – rejected,Parked,Published,Withdrawn"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D81" type="list">
@@ -8761,49 +8774,49 @@
   <sheetData>
     <row r="1" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="27" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" s="27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D1" s="27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E1" s="27" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F1" s="27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G1" s="27" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H1" s="27" t="s">
         <v>62</v>
       </c>
       <c r="I1" s="27" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J1" s="28" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K1" s="28" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="L1" s="28" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M1" s="28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N1" s="28" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O1" s="28" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8811,13 +8824,13 @@
         <v>65</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C2" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E2" s="34" t="n">
         <v>45463</v>
@@ -8830,10 +8843,10 @@
         <v>144</v>
       </c>
       <c r="H2" s="29" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I2" s="33" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J2" s="32" t="n">
         <f aca="false">IF(OR(D2="",D2="Planned"),0,1)</f>
@@ -8865,13 +8878,13 @@
         <v>65</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E3" s="34" t="n">
         <v>45630</v>
@@ -8915,13 +8928,13 @@
         <v>65</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" s="34" t="n">
         <v>45656</v>
@@ -8965,13 +8978,13 @@
         <v>65</v>
       </c>
       <c r="B5" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C5" s="33" t="s">
-        <v>141</v>
-      </c>
       <c r="D5" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E5" s="34" t="n">
         <v>45761</v>
@@ -9015,13 +9028,13 @@
         <v>65</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C6" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E6" s="34" t="n">
         <v>45761</v>
@@ -9065,13 +9078,13 @@
         <v>65</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E7" s="34" t="n">
         <v>45779</v>
@@ -9115,13 +9128,13 @@
         <v>65</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E8" s="34" t="n">
         <v>45812</v>
@@ -9132,7 +9145,7 @@
         <v>494</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I8" s="33"/>
       <c r="J8" s="32" t="n">
@@ -9165,13 +9178,13 @@
         <v>65</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="34"/>
@@ -9180,7 +9193,7 @@
         <v/>
       </c>
       <c r="H9" s="29" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I9" s="33"/>
       <c r="J9" s="32" t="n">
@@ -9213,13 +9226,13 @@
         <v>65</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
@@ -9259,13 +9272,13 @@
         <v>65</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="34"/>
@@ -9305,13 +9318,13 @@
         <v>65</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
@@ -9351,11 +9364,11 @@
         <v>65</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="33"/>
       <c r="D13" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
@@ -9395,11 +9408,11 @@
         <v>65</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="33"/>
       <c r="D14" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
@@ -9439,11 +9452,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="33"/>
       <c r="D15" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
@@ -9483,13 +9496,13 @@
         <v>70</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C16" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E16" s="34" t="n">
         <v>46296</v>
@@ -9523,7 +9536,7 @@
       </c>
       <c r="O16" s="32" t="n">
         <f aca="false">IF(N16="","",RANK(N16,$N$2:$N$1000))</f>
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9531,13 +9544,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="34"/>
@@ -9577,13 +9590,13 @@
         <v>70</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="34"/>
@@ -9623,13 +9636,13 @@
         <v>72</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E19" s="34" t="n">
         <v>45457</v>
@@ -9643,7 +9656,7 @@
       </c>
       <c r="H19" s="29"/>
       <c r="I19" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J19" s="32" t="n">
         <f aca="false">IF(OR(D19="",D19="Planned"),0,1)</f>
@@ -9675,13 +9688,13 @@
         <v>72</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E20" s="34" t="n">
         <v>45464</v>
@@ -9694,7 +9707,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="29" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I20" s="33"/>
       <c r="J20" s="32" t="n">
@@ -9727,13 +9740,13 @@
         <v>72</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E21" s="34" t="n">
         <v>45464</v>
@@ -9777,13 +9790,13 @@
         <v>72</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C22" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22" s="34" t="n">
         <v>45468</v>
@@ -9796,7 +9809,7 @@
         <v>98</v>
       </c>
       <c r="H22" s="29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="I22" s="33"/>
       <c r="J22" s="32" t="n">
@@ -9829,11 +9842,11 @@
         <v>72</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C23" s="33"/>
       <c r="D23" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E23" s="34" t="n">
         <v>45531</v>
@@ -9846,7 +9859,7 @@
         <v>2</v>
       </c>
       <c r="H23" s="29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I23" s="33"/>
       <c r="J23" s="32" t="n">
@@ -9879,13 +9892,13 @@
         <v>72</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C24" s="33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E24" s="34" t="n">
         <v>45566</v>
@@ -9898,10 +9911,10 @@
         <v>0</v>
       </c>
       <c r="H24" s="29" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I24" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J24" s="32" t="n">
         <f aca="false">IF(OR(D24="",D24="Planned"),0,1)</f>
@@ -9933,13 +9946,13 @@
         <v>72</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E25" s="34" t="n">
         <v>45567</v>
@@ -9952,7 +9965,7 @@
         <v>4</v>
       </c>
       <c r="H25" s="29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I25" s="33"/>
       <c r="J25" s="32" t="n">
@@ -9985,11 +9998,11 @@
         <v>72</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C26" s="33"/>
       <c r="D26" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E26" s="34" t="n">
         <v>45579</v>
@@ -10033,13 +10046,13 @@
         <v>72</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E27" s="34" t="n">
         <v>45630</v>
@@ -10083,11 +10096,11 @@
         <v>72</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C28" s="33"/>
       <c r="D28" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E28" s="34" t="n">
         <v>45667</v>
@@ -10131,11 +10144,11 @@
         <v>72</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C29" s="33"/>
       <c r="D29" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E29" s="34" t="n">
         <v>45747</v>
@@ -10179,13 +10192,13 @@
         <v>72</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C30" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E30" s="34" t="n">
         <v>45754</v>
@@ -10198,10 +10211,10 @@
         <v>12</v>
       </c>
       <c r="H30" s="29" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I30" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J30" s="32" t="n">
         <f aca="false">IF(OR(D30="",D30="Planned"),0,1)</f>
@@ -10233,11 +10246,11 @@
         <v>72</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C31" s="33"/>
       <c r="D31" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E31" s="34" t="n">
         <v>45754</v>
@@ -10281,13 +10294,13 @@
         <v>72</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C32" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E32" s="34" t="n">
         <v>45768</v>
@@ -10300,7 +10313,7 @@
         <v>99</v>
       </c>
       <c r="H32" s="29" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I32" s="33"/>
       <c r="J32" s="32" t="n">
@@ -10333,13 +10346,13 @@
         <v>72</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E33" s="34" t="n">
         <v>45799</v>
@@ -10353,7 +10366,7 @@
       </c>
       <c r="H33" s="29"/>
       <c r="I33" s="33" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J33" s="32" t="n">
         <f aca="false">IF(OR(D33="",D33="Planned"),0,1)</f>
@@ -10385,13 +10398,13 @@
         <v>72</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E34" s="34" t="n">
         <v>45830</v>
@@ -10405,7 +10418,7 @@
       </c>
       <c r="H34" s="29"/>
       <c r="I34" s="33" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J34" s="32" t="n">
         <f aca="false">IF(OR(D34="",D34="Planned"),0,1)</f>
@@ -10437,13 +10450,13 @@
         <v>72</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E35" s="34" t="n">
         <v>46289</v>
@@ -10454,7 +10467,7 @@
         <v>17</v>
       </c>
       <c r="H35" s="29" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I35" s="33" t="s">
         <v>73</v>
@@ -10481,7 +10494,7 @@
       </c>
       <c r="O35" s="32" t="n">
         <f aca="false">IF(N35="","",RANK(N35,$N$2:$N$1000))</f>
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10489,13 +10502,13 @@
         <v>72</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C36" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E36" s="34"/>
       <c r="F36" s="34"/>
@@ -10504,7 +10517,7 @@
         <v/>
       </c>
       <c r="H36" s="29" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="I36" s="33"/>
       <c r="J36" s="32" t="n">
@@ -10537,13 +10550,13 @@
         <v>72</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
@@ -10552,7 +10565,7 @@
         <v/>
       </c>
       <c r="H37" s="29" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I37" s="33"/>
       <c r="J37" s="32" t="n">
@@ -10585,13 +10598,13 @@
         <v>72</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C38" s="33" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="34"/>
@@ -10600,7 +10613,7 @@
         <v/>
       </c>
       <c r="H38" s="29" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="I38" s="33"/>
       <c r="J38" s="32" t="n">
@@ -10633,11 +10646,11 @@
         <v>72</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C39" s="33"/>
       <c r="D39" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E39" s="34"/>
       <c r="F39" s="34"/>
@@ -10646,7 +10659,7 @@
         <v/>
       </c>
       <c r="H39" s="29" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="I39" s="33"/>
       <c r="J39" s="32" t="n">
@@ -10679,11 +10692,11 @@
         <v>72</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C40" s="33"/>
       <c r="D40" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E40" s="34"/>
       <c r="F40" s="34"/>
@@ -10692,7 +10705,7 @@
         <v/>
       </c>
       <c r="H40" s="29" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I40" s="33"/>
       <c r="J40" s="32" t="n">
@@ -10725,11 +10738,11 @@
         <v>72</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C41" s="33"/>
       <c r="D41" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E41" s="34"/>
       <c r="F41" s="34"/>
@@ -10738,7 +10751,7 @@
         <v/>
       </c>
       <c r="H41" s="29" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I41" s="33"/>
       <c r="J41" s="32" t="n">
@@ -10771,13 +10784,13 @@
         <v>72</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C42" s="33" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E42" s="34"/>
       <c r="F42" s="34"/>
@@ -10786,7 +10799,7 @@
         <v/>
       </c>
       <c r="H42" s="29" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="I42" s="33"/>
       <c r="J42" s="32" t="n">
@@ -10819,13 +10832,13 @@
         <v>72</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E43" s="34"/>
       <c r="F43" s="34"/>
@@ -10865,13 +10878,13 @@
         <v>72</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C44" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D44" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E44" s="34"/>
       <c r="F44" s="34"/>
@@ -10880,7 +10893,7 @@
         <v/>
       </c>
       <c r="H44" s="29" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I44" s="33"/>
       <c r="J44" s="32" t="n">
@@ -10913,13 +10926,13 @@
         <v>72</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C45" s="33" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D45" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E45" s="34"/>
       <c r="F45" s="34"/>
@@ -10959,13 +10972,13 @@
         <v>72</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C46" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D46" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E46" s="34"/>
       <c r="F46" s="34"/>
@@ -11005,13 +11018,13 @@
         <v>72</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D47" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E47" s="34"/>
       <c r="F47" s="34"/>
@@ -11051,13 +11064,13 @@
         <v>72</v>
       </c>
       <c r="B48" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="C48" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="C48" s="33" t="s">
-        <v>214</v>
-      </c>
       <c r="D48" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E48" s="34"/>
       <c r="F48" s="34"/>
@@ -11097,13 +11110,13 @@
         <v>72</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E49" s="34"/>
       <c r="F49" s="34"/>
@@ -11143,11 +11156,11 @@
         <v>72</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C50" s="33"/>
       <c r="D50" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E50" s="34"/>
       <c r="F50" s="34"/>
@@ -11187,11 +11200,11 @@
         <v>72</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C51" s="33"/>
       <c r="D51" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E51" s="34"/>
       <c r="F51" s="34"/>
@@ -11231,11 +11244,11 @@
         <v>72</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C52" s="33"/>
       <c r="D52" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E52" s="34"/>
       <c r="F52" s="34"/>
@@ -11275,11 +11288,11 @@
         <v>72</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C53" s="33"/>
       <c r="D53" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E53" s="34"/>
       <c r="F53" s="34"/>
@@ -11319,11 +11332,11 @@
         <v>72</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C54" s="33"/>
       <c r="D54" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E54" s="34"/>
       <c r="F54" s="34"/>
@@ -11363,11 +11376,11 @@
         <v>72</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C55" s="33"/>
       <c r="D55" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E55" s="34"/>
       <c r="F55" s="34"/>
@@ -11407,11 +11420,11 @@
         <v>72</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C56" s="33"/>
       <c r="D56" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E56" s="34"/>
       <c r="F56" s="34"/>
@@ -11451,11 +11464,11 @@
         <v>72</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C57" s="33"/>
       <c r="D57" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E57" s="34"/>
       <c r="F57" s="34"/>
@@ -11495,13 +11508,13 @@
         <v>72</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C58" s="33" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D58" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E58" s="34"/>
       <c r="F58" s="34"/>
@@ -11541,11 +11554,11 @@
         <v>75</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C59" s="33"/>
       <c r="D59" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E59" s="34" t="n">
         <v>46178</v>
@@ -11559,7 +11572,7 @@
       </c>
       <c r="H59" s="29"/>
       <c r="I59" s="33" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J59" s="32" t="n">
         <f aca="false">IF(OR(D59="",D59="Planned"),0,1)</f>
@@ -11591,13 +11604,13 @@
         <v>75</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C60" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D60" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E60" s="34" t="n">
         <v>46200</v>
@@ -11643,13 +11656,13 @@
         <v>77</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C61" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D61" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E61" s="34" t="n">
         <v>46295</v>
@@ -11693,13 +11706,13 @@
         <v>77</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C62" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D62" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E62" s="34" t="n">
         <v>46296</v>
@@ -11743,13 +11756,13 @@
         <v>77</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C63" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D63" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E63" s="34" t="n">
         <v>46300</v>
@@ -11783,7 +11796,7 @@
       </c>
       <c r="O63" s="32" t="n">
         <f aca="false">IF(N63="","",RANK(N63,$N$2:$N$1000))</f>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -11791,13 +11804,13 @@
         <v>77</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C64" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D64" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E64" s="34"/>
       <c r="F64" s="34"/>
@@ -11837,11 +11850,11 @@
         <v>77</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C65" s="33"/>
       <c r="D65" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E65" s="34"/>
       <c r="F65" s="34"/>
@@ -11881,13 +11894,13 @@
         <v>77</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C66" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D66" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E66" s="34"/>
       <c r="F66" s="34"/>
@@ -11927,13 +11940,13 @@
         <v>79</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C67" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D67" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E67" s="34"/>
       <c r="F67" s="34"/>
@@ -11942,7 +11955,7 @@
         <v/>
       </c>
       <c r="H67" s="29" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I67" s="33"/>
       <c r="J67" s="32" t="n">
@@ -11975,13 +11988,13 @@
         <v>81</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C68" s="33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D68" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E68" s="34" t="n">
         <v>46300</v>
@@ -11994,7 +12007,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I68" s="33"/>
       <c r="J68" s="32" t="n">
@@ -12027,13 +12040,13 @@
         <v>81</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C69" s="33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D69" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E69" s="34" t="n">
         <v>46301</v>
@@ -12067,7 +12080,7 @@
       </c>
       <c r="O69" s="32" t="n">
         <f aca="false">IF(N69="","",RANK(N69,$N$2:$N$1000))</f>
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12075,13 +12088,13 @@
         <v>81</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D70" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E70" s="34"/>
       <c r="F70" s="34"/>
@@ -12121,11 +12134,11 @@
         <v>83</v>
       </c>
       <c r="B71" s="33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C71" s="33"/>
       <c r="D71" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E71" s="34" t="n">
         <v>46258</v>
@@ -12166,16 +12179,16 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B72" s="33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C72" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D72" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E72" s="34" t="n">
         <v>45774</v>
@@ -12189,7 +12202,7 @@
       </c>
       <c r="H72" s="29"/>
       <c r="I72" s="33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J72" s="32" t="n">
         <f aca="false">IF(OR(D72="",D72="Planned"),0,1)</f>
@@ -12218,16 +12231,16 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B73" s="33" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C73" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D73" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E73" s="34" t="n">
         <v>45842</v>
@@ -12240,7 +12253,7 @@
         <v>11</v>
       </c>
       <c r="H73" s="29" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I73" s="33"/>
       <c r="J73" s="32" t="n">
@@ -12270,16 +12283,16 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B74" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C74" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E74" s="34" t="n">
         <v>45853</v>
@@ -12292,7 +12305,7 @@
         <v>183</v>
       </c>
       <c r="H74" s="29" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I74" s="33"/>
       <c r="J74" s="32" t="n">
@@ -12322,16 +12335,16 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C75" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E75" s="34" t="n">
         <v>46037</v>
@@ -12344,7 +12357,7 @@
         <v>5</v>
       </c>
       <c r="H75" s="29" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I75" s="33"/>
       <c r="J75" s="32" t="n">
@@ -12374,16 +12387,16 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B76" s="33" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C76" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D76" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E76" s="34" t="n">
         <v>46042</v>
@@ -12424,16 +12437,16 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B77" s="33" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C77" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E77" s="34" t="n">
         <v>46063</v>
@@ -12474,16 +12487,16 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B78" s="33" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C78" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E78" s="34" t="n">
         <v>46063</v>
@@ -12496,7 +12509,7 @@
         <v>69</v>
       </c>
       <c r="H78" s="29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I78" s="33"/>
       <c r="J78" s="32" t="n">
@@ -12526,16 +12539,16 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B79" s="33" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C79" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E79" s="34" t="n">
         <v>46153</v>
@@ -12569,21 +12582,21 @@
       </c>
       <c r="O79" s="32" t="n">
         <f aca="false">IF(N79="","",RANK(N79,$N$2:$N$1000))</f>
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B80" s="33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C80" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D80" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E80" s="34"/>
       <c r="F80" s="34"/>
@@ -12620,16 +12633,16 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B81" s="33" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C81" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D81" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E81" s="34"/>
       <c r="F81" s="34"/>
@@ -12666,16 +12679,16 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B82" s="33" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C82" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D82" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E82" s="34"/>
       <c r="F82" s="34"/>
@@ -12712,16 +12725,16 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B83" s="33" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C83" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D83" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E83" s="34"/>
       <c r="F83" s="34"/>
@@ -12730,7 +12743,7 @@
         <v/>
       </c>
       <c r="H83" s="29" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I83" s="33"/>
       <c r="J83" s="32" t="n">
@@ -12760,16 +12773,16 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B84" s="33" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C84" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D84" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E84" s="34"/>
       <c r="F84" s="34"/>
@@ -12806,16 +12819,16 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B85" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C85" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D85" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E85" s="34"/>
       <c r="F85" s="34"/>
@@ -12852,16 +12865,16 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B86" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C86" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D86" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E86" s="34"/>
       <c r="F86" s="34"/>
@@ -12898,16 +12911,16 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" s="33" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C87" s="33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D87" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E87" s="34"/>
       <c r="F87" s="34"/>
@@ -12944,16 +12957,16 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="33" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B88" s="33" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C88" s="33" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D88" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E88" s="34"/>
       <c r="F88" s="34"/>
@@ -12990,16 +13003,16 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B89" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C89" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D89" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E89" s="34" t="n">
         <v>45419</v>
@@ -13012,7 +13025,7 @@
         <v>193</v>
       </c>
       <c r="H89" s="29" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I89" s="33"/>
       <c r="J89" s="32" t="n">
@@ -13042,16 +13055,16 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="33" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C90" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D90" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E90" s="34" t="n">
         <v>45759</v>
@@ -13092,14 +13105,14 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B91" s="33" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C91" s="33"/>
       <c r="D91" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E91" s="34" t="n">
         <v>45759</v>
@@ -13140,16 +13153,16 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B92" s="33" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C92" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D92" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E92" s="34" t="n">
         <v>45761</v>
@@ -13162,7 +13175,7 @@
         <v>54</v>
       </c>
       <c r="H92" s="29" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I92" s="33"/>
       <c r="J92" s="32" t="n">
@@ -13192,16 +13205,16 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B93" s="33" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C93" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D93" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E93" s="34" t="n">
         <v>45844</v>
@@ -13215,7 +13228,7 @@
       </c>
       <c r="H93" s="29"/>
       <c r="I93" s="33" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="J93" s="32" t="n">
         <f aca="false">IF(OR(D93="",D93="Planned"),0,1)</f>
@@ -13244,16 +13257,16 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B94" s="33" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C94" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D94" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E94" s="34" t="n">
         <v>45845</v>
@@ -13266,10 +13279,10 @@
         <v>10</v>
       </c>
       <c r="H94" s="29" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I94" s="33" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J94" s="32" t="n">
         <f aca="false">IF(OR(D94="",D94="Planned"),0,1)</f>
@@ -13298,16 +13311,16 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B95" s="33" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C95" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D95" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E95" s="34" t="n">
         <v>45855</v>
@@ -13348,16 +13361,16 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B96" s="33" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C96" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D96" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E96" s="34" t="n">
         <v>45863</v>
@@ -13398,16 +13411,16 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B97" s="33" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C97" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D97" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E97" s="34" t="n">
         <v>45903</v>
@@ -13448,16 +13461,16 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B98" s="33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C98" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D98" s="33" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E98" s="34" t="n">
         <v>46184</v>
@@ -13470,7 +13483,7 @@
         <v>45</v>
       </c>
       <c r="H98" s="29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="I98" s="33"/>
       <c r="J98" s="32" t="n">
@@ -13500,16 +13513,16 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B99" s="33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C99" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D99" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E99" s="34" t="n">
         <v>46232</v>
@@ -13520,7 +13533,7 @@
         <v>74</v>
       </c>
       <c r="H99" s="29" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="I99" s="33"/>
       <c r="J99" s="32" t="n">
@@ -13545,21 +13558,21 @@
       </c>
       <c r="O99" s="32" t="n">
         <f aca="false">IF(N99="","",RANK(N99,$N$2:$N$1000))</f>
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B100" s="33" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C100" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D100" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E100" s="34"/>
       <c r="F100" s="34"/>
@@ -13596,16 +13609,16 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B101" s="33" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C101" s="33" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D101" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E101" s="34"/>
       <c r="F101" s="34"/>
@@ -13642,16 +13655,16 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B102" s="33" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C102" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D102" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E102" s="34"/>
       <c r="F102" s="34"/>
@@ -13688,16 +13701,16 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B103" s="33" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C103" s="33" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D103" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E103" s="34"/>
       <c r="F103" s="34"/>
@@ -13734,16 +13747,16 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B104" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C104" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D104" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E104" s="34" t="n">
         <v>46245</v>
@@ -13757,7 +13770,7 @@
       </c>
       <c r="H104" s="29"/>
       <c r="I104" s="33" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="J104" s="32" t="n">
         <f aca="false">IF(OR(D104="",D104="Planned"),0,1)</f>
@@ -13786,16 +13799,16 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B105" s="33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C105" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D105" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E105" s="34" t="n">
         <v>46246</v>
@@ -13836,16 +13849,16 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B106" s="33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C106" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D106" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E106" s="34" t="n">
         <v>46280</v>
@@ -13886,16 +13899,16 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B107" s="33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C107" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D107" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E107" s="34" t="n">
         <v>46283</v>
@@ -13908,7 +13921,7 @@
         <v>0</v>
       </c>
       <c r="H107" s="29" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I107" s="33"/>
       <c r="J107" s="32" t="n">
@@ -13938,16 +13951,16 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B108" s="33" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C108" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D108" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E108" s="34" t="n">
         <v>46300</v>
@@ -13988,16 +14001,16 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B109" s="33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C109" s="33" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D109" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E109" s="34"/>
       <c r="F109" s="34"/>
@@ -14006,7 +14019,7 @@
         <v/>
       </c>
       <c r="H109" s="29" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I109" s="33"/>
       <c r="J109" s="32" t="n">
@@ -14036,16 +14049,16 @@
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B110" s="33" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C110" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D110" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E110" s="34"/>
       <c r="F110" s="34"/>
@@ -14082,16 +14095,16 @@
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B111" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C111" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D111" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E111" s="34"/>
       <c r="F111" s="34"/>
@@ -14128,16 +14141,16 @@
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B112" s="33" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C112" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D112" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E112" s="34"/>
       <c r="F112" s="34"/>
@@ -14174,16 +14187,16 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B113" s="33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C113" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D113" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E113" s="34"/>
       <c r="F113" s="34"/>
@@ -14220,16 +14233,16 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B114" s="33" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C114" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D114" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E114" s="34"/>
       <c r="F114" s="34"/>
@@ -14266,16 +14279,16 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B115" s="33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C115" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D115" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E115" s="34"/>
       <c r="F115" s="34"/>
@@ -14312,16 +14325,16 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B116" s="33" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C116" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D116" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E116" s="34"/>
       <c r="F116" s="34"/>
@@ -14358,16 +14371,16 @@
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B117" s="33" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C117" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D117" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E117" s="34"/>
       <c r="F117" s="34"/>
@@ -14404,16 +14417,16 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B118" s="33" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C118" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D118" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E118" s="34"/>
       <c r="F118" s="34"/>
@@ -14450,16 +14463,16 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B119" s="33" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C119" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D119" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E119" s="34"/>
       <c r="F119" s="34"/>
@@ -14496,16 +14509,16 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B120" s="33" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C120" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D120" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E120" s="34"/>
       <c r="F120" s="34"/>
@@ -14542,16 +14555,16 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B121" s="33" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C121" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D121" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E121" s="34"/>
       <c r="F121" s="34"/>
@@ -14588,16 +14601,16 @@
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="33" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B122" s="33" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C122" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D122" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E122" s="34"/>
       <c r="F122" s="34"/>
@@ -14634,16 +14647,16 @@
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B123" s="33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C123" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D123" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E123" s="34" t="n">
         <v>45474</v>
@@ -14684,16 +14697,16 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B124" s="33" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C124" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D124" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E124" s="34" t="n">
         <v>45500</v>
@@ -14706,7 +14719,7 @@
         <v>11</v>
       </c>
       <c r="H124" s="29" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I124" s="33"/>
       <c r="J124" s="32" t="n">
@@ -14736,16 +14749,16 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B125" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C125" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D125" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E125" s="34" t="n">
         <v>45501</v>
@@ -14758,7 +14771,7 @@
         <v>2</v>
       </c>
       <c r="H125" s="29" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="I125" s="33"/>
       <c r="J125" s="32" t="n">
@@ -14788,16 +14801,16 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B126" s="33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C126" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D126" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E126" s="34" t="n">
         <v>45509</v>
@@ -14810,7 +14823,7 @@
         <v>11</v>
       </c>
       <c r="H126" s="29" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I126" s="33"/>
       <c r="J126" s="32" t="n">
@@ -14840,16 +14853,16 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B127" s="33" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C127" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D127" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E127" s="34" t="n">
         <v>45512</v>
@@ -14890,16 +14903,16 @@
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B128" s="33" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C128" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D128" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E128" s="34" t="n">
         <v>45518</v>
@@ -14912,7 +14925,7 @@
         <v>6</v>
       </c>
       <c r="H128" s="29" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I128" s="33"/>
       <c r="J128" s="32" t="n">
@@ -14942,16 +14955,16 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B129" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="C129" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="C129" s="33" t="s">
-        <v>141</v>
-      </c>
       <c r="D129" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E129" s="34" t="n">
         <v>45525</v>
@@ -14992,16 +15005,16 @@
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B130" s="33" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C130" s="33" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D130" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E130" s="34" t="n">
         <v>45525</v>
@@ -15014,7 +15027,7 @@
         <v>7</v>
       </c>
       <c r="H130" s="29" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I130" s="33"/>
       <c r="J130" s="32" t="n">
@@ -15044,16 +15057,16 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B131" s="33" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C131" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D131" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E131" s="34" t="n">
         <v>45525</v>
@@ -15094,16 +15107,16 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B132" s="33" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C132" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D132" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E132" s="34" t="n">
         <v>45525</v>
@@ -15116,7 +15129,7 @@
         <v>30</v>
       </c>
       <c r="H132" s="29" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I132" s="33"/>
       <c r="J132" s="32" t="n">
@@ -15146,16 +15159,16 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B133" s="33" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C133" s="33" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D133" s="33" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E133" s="34" t="n">
         <v>45630</v>
@@ -15168,7 +15181,7 @@
         <v>238</v>
       </c>
       <c r="H133" s="29" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="I133" s="33"/>
       <c r="J133" s="32" t="n">
@@ -15198,16 +15211,16 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B134" s="33" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C134" s="33" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="D134" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E134" s="34" t="n">
         <v>45782</v>
@@ -15248,16 +15261,16 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B135" s="33" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C135" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D135" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E135" s="34" t="n">
         <v>45784</v>
@@ -15298,16 +15311,16 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B136" s="33" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C136" s="33" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D136" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E136" s="34" t="n">
         <v>46045</v>
@@ -15318,7 +15331,7 @@
         <v>261</v>
       </c>
       <c r="H136" s="29" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I136" s="33"/>
       <c r="J136" s="32" t="n">
@@ -15343,21 +15356,21 @@
       </c>
       <c r="O136" s="32" t="n">
         <f aca="false">IF(N136="","",RANK(N136,$N$2:$N$1000))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B137" s="33" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C137" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D137" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E137" s="34" t="n">
         <v>46273</v>
@@ -15398,16 +15411,16 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B138" s="33" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C138" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D138" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E138" s="34" t="n">
         <v>46280</v>
@@ -15448,16 +15461,16 @@
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B139" s="33" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C139" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D139" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E139" s="34"/>
       <c r="F139" s="34"/>
@@ -15466,7 +15479,7 @@
         <v/>
       </c>
       <c r="H139" s="29" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="I139" s="33"/>
       <c r="J139" s="32" t="n">
@@ -15496,16 +15509,16 @@
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B140" s="33" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C140" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D140" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E140" s="34"/>
       <c r="F140" s="34"/>
@@ -15514,7 +15527,7 @@
         <v/>
       </c>
       <c r="H140" s="29" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="I140" s="33"/>
       <c r="J140" s="32" t="n">
@@ -15544,16 +15557,16 @@
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B141" s="33" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C141" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D141" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E141" s="34"/>
       <c r="F141" s="34"/>
@@ -15590,16 +15603,16 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B142" s="33" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C142" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D142" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E142" s="34"/>
       <c r="F142" s="34"/>
@@ -15608,7 +15621,7 @@
         <v/>
       </c>
       <c r="H142" s="29" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="I142" s="33"/>
       <c r="J142" s="32" t="n">
@@ -15638,16 +15651,16 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B143" s="33" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C143" s="33" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D143" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E143" s="34"/>
       <c r="F143" s="34"/>
@@ -15656,7 +15669,7 @@
         <v/>
       </c>
       <c r="H143" s="29" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I143" s="33"/>
       <c r="J143" s="32" t="n">
@@ -15686,16 +15699,16 @@
     </row>
     <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B144" s="33" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C144" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D144" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E144" s="34"/>
       <c r="F144" s="34"/>
@@ -15732,14 +15745,14 @@
     </row>
     <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B145" s="33" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C145" s="33"/>
       <c r="D145" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E145" s="34"/>
       <c r="F145" s="34"/>
@@ -15776,16 +15789,16 @@
     </row>
     <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B146" s="33" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C146" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D146" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E146" s="34"/>
       <c r="F146" s="34"/>
@@ -15794,7 +15807,7 @@
         <v/>
       </c>
       <c r="H146" s="29" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I146" s="33"/>
       <c r="J146" s="32" t="n">
@@ -15824,16 +15837,16 @@
     </row>
     <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B147" s="33" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C147" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D147" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
@@ -15870,16 +15883,16 @@
     </row>
     <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B148" s="33" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C148" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D148" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E148" s="34"/>
       <c r="F148" s="34"/>
@@ -15916,16 +15929,16 @@
     </row>
     <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B149" s="33" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C149" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D149" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E149" s="34"/>
       <c r="F149" s="34"/>
@@ -15934,7 +15947,7 @@
         <v/>
       </c>
       <c r="H149" s="29" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="I149" s="33"/>
       <c r="J149" s="32" t="n">
@@ -15964,16 +15977,16 @@
     </row>
     <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B150" s="33" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C150" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D150" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E150" s="34"/>
       <c r="F150" s="34"/>
@@ -16010,16 +16023,16 @@
     </row>
     <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B151" s="33" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C151" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D151" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E151" s="34"/>
       <c r="F151" s="34"/>
@@ -16056,16 +16069,16 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B152" s="33" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C152" s="33" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D152" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E152" s="34"/>
       <c r="F152" s="34"/>
@@ -16074,7 +16087,7 @@
         <v/>
       </c>
       <c r="H152" s="29" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I152" s="33"/>
       <c r="J152" s="32" t="n">
@@ -16104,16 +16117,16 @@
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B153" s="33" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C153" s="33" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D153" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E153" s="34"/>
       <c r="F153" s="34"/>
@@ -16122,7 +16135,7 @@
         <v/>
       </c>
       <c r="H153" s="29" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="I153" s="33"/>
       <c r="J153" s="32" t="n">
@@ -16152,16 +16165,16 @@
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B154" s="33" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C154" s="33" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="D154" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E154" s="34"/>
       <c r="F154" s="34"/>
@@ -16170,7 +16183,7 @@
         <v/>
       </c>
       <c r="H154" s="29" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="I154" s="33"/>
       <c r="J154" s="32" t="n">
@@ -16200,16 +16213,16 @@
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B155" s="33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C155" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D155" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E155" s="34"/>
       <c r="F155" s="34"/>
@@ -16246,14 +16259,14 @@
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B156" s="33" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C156" s="33"/>
       <c r="D156" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E156" s="34"/>
       <c r="F156" s="34"/>
@@ -16290,14 +16303,14 @@
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B157" s="33" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C157" s="33"/>
       <c r="D157" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E157" s="34" t="n">
         <v>45824</v>
@@ -16338,14 +16351,14 @@
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B158" s="33" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C158" s="33"/>
       <c r="D158" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E158" s="34" t="n">
         <v>45834</v>
@@ -16386,14 +16399,14 @@
     </row>
     <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B159" s="33" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C159" s="33"/>
       <c r="D159" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E159" s="34" t="n">
         <v>45841</v>
@@ -16434,14 +16447,14 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B160" s="33" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C160" s="33"/>
       <c r="D160" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E160" s="34"/>
       <c r="F160" s="34"/>
@@ -16478,16 +16491,16 @@
     </row>
     <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B161" s="33" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C161" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D161" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E161" s="34" t="n">
         <v>46300</v>
@@ -16521,21 +16534,21 @@
       </c>
       <c r="O161" s="32" t="n">
         <f aca="false">IF(N161="","",RANK(N161,$N$2:$N$1000))</f>
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B162" s="33" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C162" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D162" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E162" s="34"/>
       <c r="F162" s="34"/>
@@ -16572,16 +16585,16 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B163" s="33" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C163" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D163" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E163" s="34"/>
       <c r="F163" s="34"/>
@@ -16618,16 +16631,16 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B164" s="33" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C164" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D164" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E164" s="34"/>
       <c r="F164" s="34"/>
@@ -16664,16 +16677,16 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B165" s="33" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C165" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D165" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E165" s="34"/>
       <c r="F165" s="34"/>
@@ -16710,16 +16723,16 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B166" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C166" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D166" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E166" s="34"/>
       <c r="F166" s="34"/>
@@ -16756,16 +16769,16 @@
     </row>
     <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="33" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B167" s="33" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C167" s="33" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D167" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E167" s="34"/>
       <c r="F167" s="34"/>
@@ -16802,16 +16815,16 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B168" s="33" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C168" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D168" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E168" s="34" t="n">
         <v>46071</v>
@@ -16852,16 +16865,16 @@
     </row>
     <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B169" s="33" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C169" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D169" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E169" s="34" t="n">
         <v>46185</v>
@@ -16902,16 +16915,16 @@
     </row>
     <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B170" s="33" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C170" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D170" s="33" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E170" s="34" t="n">
         <v>46303</v>
@@ -16945,19 +16958,19 @@
       </c>
       <c r="O170" s="32" t="n">
         <f aca="false">IF(N170="","",RANK(N170,$N$2:$N$1000))</f>
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B171" s="33" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C171" s="33"/>
       <c r="D171" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E171" s="34"/>
       <c r="F171" s="34"/>
@@ -16994,14 +17007,14 @@
     </row>
     <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B172" s="33" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C172" s="33"/>
       <c r="D172" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E172" s="34"/>
       <c r="F172" s="34"/>
@@ -17038,14 +17051,14 @@
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B173" s="33" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C173" s="33"/>
       <c r="D173" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E173" s="34"/>
       <c r="F173" s="34"/>
@@ -17082,16 +17095,16 @@
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B174" s="33" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C174" s="33" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="D174" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E174" s="34"/>
       <c r="F174" s="34"/>
@@ -17128,16 +17141,16 @@
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B175" s="33" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C175" s="33" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D175" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E175" s="34"/>
       <c r="F175" s="34"/>
@@ -17174,16 +17187,16 @@
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B176" s="33" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C176" s="33" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D176" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E176" s="34"/>
       <c r="F176" s="34"/>
@@ -17220,16 +17233,16 @@
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B177" s="33" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C177" s="33" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D177" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E177" s="34"/>
       <c r="F177" s="34"/>
@@ -17238,7 +17251,7 @@
         <v/>
       </c>
       <c r="H177" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I177" s="33"/>
       <c r="J177" s="32" t="n">
@@ -17268,16 +17281,16 @@
     </row>
     <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B178" s="33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C178" s="33" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D178" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E178" s="34"/>
       <c r="F178" s="34"/>
@@ -17314,16 +17327,16 @@
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B179" s="33" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C179" s="33" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D179" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E179" s="34"/>
       <c r="F179" s="34"/>
@@ -17360,14 +17373,14 @@
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B180" s="33" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C180" s="33"/>
       <c r="D180" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E180" s="34"/>
       <c r="F180" s="34"/>
@@ -17404,14 +17417,14 @@
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="33" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B181" s="33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C181" s="33"/>
       <c r="D181" s="33" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E181" s="34"/>
       <c r="F181" s="34"/>
@@ -17448,14 +17461,14 @@
     </row>
     <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B182" s="33" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C182" s="33"/>
       <c r="D182" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E182" s="34" t="n">
         <v>45671</v>
@@ -17496,14 +17509,14 @@
     </row>
     <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="33" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B183" s="33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C183" s="33"/>
       <c r="D183" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E183" s="34" t="n">
         <v>45457</v>
@@ -17516,7 +17529,7 @@
         <v>242</v>
       </c>
       <c r="H183" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I183" s="33"/>
       <c r="J183" s="32" t="n">
@@ -17546,14 +17559,14 @@
     </row>
     <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B184" s="33" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C184" s="33"/>
       <c r="D184" s="33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E184" s="34" t="n">
         <v>45759</v>
@@ -17566,7 +17579,7 @@
         <v>206</v>
       </c>
       <c r="H184" s="29" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="I184" s="33"/>
       <c r="J184" s="32" t="n">
@@ -17596,38 +17609,44 @@
     </row>
     <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="33" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B185" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C185" s="33"/>
       <c r="D185" s="33" t="s">
-        <v>151</v>
-      </c>
-      <c r="E185" s="34"/>
-      <c r="F185" s="34"/>
-      <c r="G185" s="35" t="str">
+        <v>137</v>
+      </c>
+      <c r="E185" s="34" t="n">
+        <v>45907</v>
+      </c>
+      <c r="F185" s="34" t="n">
+        <v>45922</v>
+      </c>
+      <c r="G185" s="35" t="n">
         <f aca="true">IF(OR(E185="",J185=0),"",IF(F185&lt;&gt;"",F185-E185,TODAY()-E185))</f>
-        <v/>
-      </c>
-      <c r="H185" s="29"/>
+        <v>15</v>
+      </c>
+      <c r="H185" s="29" t="s">
+        <v>368</v>
+      </c>
       <c r="I185" s="33"/>
       <c r="J185" s="32" t="n">
         <f aca="false">IF(OR(D185="",D185="Planned"),0,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" s="32" t="n">
         <f aca="false">IF(OR(D185="Under review",D185="Revision requested"),1,0)</f>
         <v>0</v>
       </c>
-      <c r="L185" s="32" t="str">
+      <c r="L185" s="36" t="n">
         <f aca="false">IF(AND(J185=1,E185&lt;&gt;""),E185+ROW()/100000,"")</f>
-        <v/>
-      </c>
-      <c r="M185" s="32" t="n">
+        <v>45907.00185</v>
+      </c>
+      <c r="M185" s="32" t="str">
         <f aca="false">IF(D185="Planned",ROW(),"")</f>
-        <v>185</v>
+        <v/>
       </c>
       <c r="N185" s="32" t="str">
         <f aca="true">IF(K185=1,IF(E185="",0,TODAY()-E185)+ROW()/100000,"")</f>
@@ -17639,18 +17658,10 @@
       </c>
     </row>
     <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B186" s="33" t="s">
-        <v>367</v>
-      </c>
-      <c r="C186" s="33" t="s">
-        <v>368</v>
-      </c>
-      <c r="D186" s="33" t="s">
-        <v>151</v>
-      </c>
+      <c r="A186" s="33"/>
+      <c r="B186" s="33"/>
+      <c r="C186" s="33"/>
+      <c r="D186" s="33"/>
       <c r="E186" s="34"/>
       <c r="F186" s="34"/>
       <c r="G186" s="35" t="str">
@@ -17671,9 +17682,9 @@
         <f aca="false">IF(AND(J186=1,E186&lt;&gt;""),E186+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="M186" s="32" t="n">
+      <c r="M186" s="32" t="str">
         <f aca="false">IF(D186="Planned",ROW(),"")</f>
-        <v>186</v>
+        <v/>
       </c>
       <c r="N186" s="32" t="str">
         <f aca="true">IF(K186=1,IF(E186="",0,TODAY()-E186)+ROW()/100000,"")</f>
@@ -17685,16 +17696,10 @@
       </c>
     </row>
     <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="33" t="s">
-        <v>115</v>
-      </c>
-      <c r="B187" s="33" t="s">
-        <v>369</v>
-      </c>
+      <c r="A187" s="33"/>
+      <c r="B187" s="33"/>
       <c r="C187" s="33"/>
-      <c r="D187" s="33" t="s">
-        <v>151</v>
-      </c>
+      <c r="D187" s="33"/>
       <c r="E187" s="34"/>
       <c r="F187" s="34"/>
       <c r="G187" s="35" t="str">
@@ -17715,9 +17720,9 @@
         <f aca="false">IF(AND(J187=1,E187&lt;&gt;""),E187+ROW()/100000,"")</f>
         <v/>
       </c>
-      <c r="M187" s="32" t="n">
+      <c r="M187" s="32" t="str">
         <f aca="false">IF(D187="Planned",ROW(),"")</f>
-        <v>187</v>
+        <v/>
       </c>
       <c r="N187" s="32" t="str">
         <f aca="true">IF(K187=1,IF(E187="",0,TODAY()-E187)+ROW()/100000,"")</f>
@@ -17729,51 +17734,41 @@
       </c>
     </row>
     <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A188" s="33" t="s">
-        <v>117</v>
-      </c>
-      <c r="B188" s="33" t="s">
-        <v>370</v>
-      </c>
+      <c r="A188" s="33"/>
+      <c r="B188" s="33"/>
       <c r="C188" s="33"/>
-      <c r="D188" s="33" t="s">
-        <v>147</v>
-      </c>
-      <c r="E188" s="34" t="n">
-        <v>45907</v>
-      </c>
+      <c r="D188" s="33"/>
+      <c r="E188" s="34"/>
       <c r="F188" s="34"/>
-      <c r="G188" s="35" t="n">
+      <c r="G188" s="35" t="str">
         <f aca="true">IF(OR(E188="",J188=0),"",IF(F188&lt;&gt;"",F188-E188,TODAY()-E188))</f>
-        <v>399</v>
-      </c>
-      <c r="H188" s="29" t="s">
-        <v>371</v>
-      </c>
+        <v/>
+      </c>
+      <c r="H188" s="29"/>
       <c r="I188" s="33"/>
       <c r="J188" s="32" t="n">
         <f aca="false">IF(OR(D188="",D188="Planned"),0,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K188" s="32" t="n">
         <f aca="false">IF(OR(D188="Under review",D188="Revision requested"),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="L188" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" s="32" t="str">
         <f aca="false">IF(AND(J188=1,E188&lt;&gt;""),E188+ROW()/100000,"")</f>
-        <v>45907.00188</v>
+        <v/>
       </c>
       <c r="M188" s="32" t="str">
         <f aca="false">IF(D188="Planned",ROW(),"")</f>
         <v/>
       </c>
-      <c r="N188" s="32" t="n">
+      <c r="N188" s="32" t="str">
         <f aca="true">IF(K188=1,IF(E188="",0,TODAY()-E188)+ROW()/100000,"")</f>
-        <v>399.00188</v>
-      </c>
-      <c r="O188" s="32" t="n">
+        <v/>
+      </c>
+      <c r="O188" s="32" t="str">
         <f aca="false">IF(N188="","",RANK(N188,$N$2:$N$1000))</f>
-        <v>2</v>
+        <v/>
       </c>
     </row>
     <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -48641,13 +48636,13 @@
     <cfRule type="cellIs" priority="3" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>"Revision requested"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="cellIs" priority="4" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Rejected"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Returned by office"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="cellIs" priority="6" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Revision resubmitted"</formula>
     </cfRule>
     <cfRule type="cellIs" priority="7" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
@@ -48656,7 +48651,7 @@
     <cfRule type="cellIs" priority="8" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="25">
       <formula>"Planned"</formula>
     </cfRule>
-    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="cellIs" priority="9" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>"Withdrawn"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48666,7 +48661,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1000">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND($K2=1,ISNUMBER($G2),$G2&gt;Dashboard!$M$3)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -48718,24 +48713,24 @@
         <v>56</v>
       </c>
       <c r="B1" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="F1" s="0" t="s">
         <v>372</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="G1" s="0" t="s">
         <v>373</v>
-      </c>
-      <c r="E1" s="0" t="s">
-        <v>374</v>
-      </c>
-      <c r="F1" s="0" t="s">
-        <v>375</v>
-      </c>
-      <c r="G1" s="0" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B2" s="0" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,A2)</f>
@@ -48760,11 +48755,11 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B3" s="0" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,A3)</f>
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D3" s="37" t="n">
         <f aca="true">EDATE(DATE(YEAR(TODAY()),3*INT((MONTH(TODAY())-1)/3)+1,1),-3*10)</f>
@@ -48785,7 +48780,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B4" s="0" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,A4)</f>
@@ -48810,11 +48805,11 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="0" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,A5)</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="37" t="n">
         <f aca="true">EDATE(DATE(YEAR(TODAY()),3*INT((MONTH(TODAY())-1)/3)+1,1),-3*8)</f>
@@ -48835,7 +48830,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B6" s="0" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,A6)</f>
@@ -48860,11 +48855,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>381</v>
+        <v>86</v>
       </c>
       <c r="B7" s="0" t="n">
         <f aca="false">COUNTIF(Papers!$F$2:$F$81,A7)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="37" t="n">
         <f aca="true">EDATE(DATE(YEAR(TODAY()),3*INT((MONTH(TODAY())-1)/3)+1,1),-3*6)</f>
@@ -48884,6 +48879,13 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>378</v>
+      </c>
+      <c r="B8" s="0" t="n">
+        <f aca="false">COUNTIF(Papers!$F$2:$F$81,A8)</f>
+        <v>0</v>
+      </c>
       <c r="D8" s="37" t="n">
         <f aca="true">EDATE(DATE(YEAR(TODAY()),3*INT((MONTH(TODAY())-1)/3)+1,1),-3*5)</f>
         <v>45839</v>
@@ -48898,7 +48900,7 @@
       </c>
       <c r="G8" s="21" t="n">
         <f aca="false">COUNTIFS(Submissions!$F$2:$F$1000,"&gt;="&amp;D8,Submissions!$F$2:$F$1000,"&lt;"&amp;EDATE(D8,3))</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
